--- a/invoice_data.xlsx
+++ b/invoice_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,30 +506,15 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>tax_type</t>
+          <t>calculated_subtotal</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>tax_rate</t>
+          <t>subtotal_match</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>tax_amount</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>calculated_subtotal</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>subtotal_match</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>tax_amount_match</t>
         </is>
@@ -541,47 +526,49 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MA109305</t>
+          <t>126757</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>KRAMW01 1202206039672</t>
-        </is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>123456789</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanpac Africa Ltd</t>
+          <t>INDUSTRIAL SUPPLIERS LTD.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>P O Box 20496 - 00200 Nairobi, Kenya
-P O Box 87025 - 80100 Mombasa, Kenya</t>
+          <t>AGA KHAN
+ROAD
+NEAR BLOOD CENTRE
+P. O. Box 97044 - 80112, MOMBASA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tel: +254 (0)20 2112100/1/2/3
-Cell : +254 (0)733 201 338, (0)722 201 338, (0)756 201 338
-Email: sansales @ sanpac.com</t>
+          <t>Tel : 041 2314147, 041 2223422
+: 041 2314518, 041 2315013
+Mobile : 0723 338476, 0735 338478
+: 0794 895749/50, 0731 768851
+E-mail . : info@jalaramkenya.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24002984</t>
+          <t>24004829</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>568980</v>
+        <v>10200</v>
       </c>
       <c r="J2" t="n">
-        <v>660016.8</v>
+        <v>11832</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -589,214 +576,31 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>91036.8</v>
+        <v>1632</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>P0005943160 x</t>
+          <t>P 051107439 Y</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Round Jerryean Yellow 10ltr</t>
+          <t>Black Gasket Maker</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>4360</v>
+        <v>60</v>
       </c>
       <c r="P2" t="n">
-        <v>118.8</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>517968</v>
-      </c>
-      <c r="U2" t="b">
+        <v>170</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>10200</v>
+      </c>
+      <c r="R2" t="b">
         <v>1</v>
       </c>
-      <c r="V2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MA109305</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>KRAMW01 1202206039672</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Sanpac Africa Ltd</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>P O Box 20496 - 00200 Nairobi, Kenya
-P O Box 87025 - 80100 Mombasa, Kenya</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Tel: +254 (0)20 2112100/1/2/3
-Cell : +254 (0)733 201 338, (0)722 201 338, (0)756 201 338
-Email: sansales @ sanpac.com</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>24002984</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>568980</v>
-      </c>
-      <c r="J3" t="n">
-        <v>660016.8</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>KES</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>91036.8</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>P0005943160 x</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Bung Cap &amp; Gasket Sky Blue</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>4360</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
-        <v>23108</v>
-      </c>
-      <c r="U3" t="b">
-        <v>1</v>
-      </c>
-      <c r="V3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>MA109305</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>KRAMW01 1202206039672</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Sanpac Africa Ltd</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>P O Box 20496 - 00200 Nairobi, Kenya
-P O Box 87025 - 80100 Mombasa, Kenya</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Tel: +254 (0)20 2112100/1/2/3
-Cell : +254 (0)733 201 338, (0)722 201 338, (0)756 201 338
-Email: sansales @ sanpac.com</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>24002984</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>568980</v>
-      </c>
-      <c r="J4" t="n">
-        <v>660016.8</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>KES</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>91036.8</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>P0005943160 x</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Woven Bags for 10ltr</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>436</v>
-      </c>
-      <c r="P4" t="n">
-        <v>64</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>VAT</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>91036.8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>27904</v>
-      </c>
-      <c r="U4" t="b">
-        <v>1</v>
-      </c>
-      <c r="V4" t="b">
+      <c r="S2" t="b">
         <v>1</v>
       </c>
     </row>

--- a/invoice_data.xlsx
+++ b/invoice_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,30 +491,45 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>vat_pin</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>unit_price</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>received on</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>calculated_subtotal</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>subtotal_match</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>tax_amount_match</t>
         </is>
@@ -526,49 +541,45 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>126757</t>
+          <t>0190276280000014247</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>123456789</v>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>KRAMW019202205027628</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>INDUSTRIAL SUPPLIERS LTD.</t>
+          <t>MEGA PACK (K) LTD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AGA KHAN
-ROAD
-NEAR BLOOD CENTRE
-P. O. Box 97044 - 80112, MOMBASA</t>
+          <t>Stanley Mathenge Road, Industrial Area
+P.O Box 3204 - 20100 Nakuru, Kenya</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tel : 041 2314147, 041 2223422
-: 041 2314518, 041 2315013
-Mobile : 0723 338476, 0735 338478
-: 0794 895749/50, 0731 768851
-E-mail . : info@jalaramkenya.com</t>
+          <t>+254 73 7839008/703833954/700781800 | megapack@megaspingroup.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24004829</t>
+          <t>24004078</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>10200</v>
+        <v>117573.81</v>
       </c>
       <c r="J2" t="n">
-        <v>11832</v>
+        <v>117573.81</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -576,32 +587,142 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1632</v>
+        <v>16217.08</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>P 051107439 Y</t>
+          <t>P051237141X</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Black Gasket Maker</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>60</v>
+          <t>P051237141X</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>PWANI - DIVA 24X200G (COMBINED VARIANTS)</t>
+        </is>
       </c>
       <c r="P2" t="n">
-        <v>170</v>
+        <v>28</v>
       </c>
       <c r="Q2" t="n">
-        <v>10200</v>
-      </c>
-      <c r="R2" t="b">
+        <v>28460</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Not Provided</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Vendor Portal</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>796880</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="b">
-        <v>1</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0190276280000014247</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>KRAMW019202205027628</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MEGA PACK (K) LTD</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stanley Mathenge Road, Industrial Area
+P.O Box 3204 - 20100 Nakuru, Kenya</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>+254 73 7839008/703833954/700781800 | megapack@megaspingroup.com</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>24004078</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>117573.81</v>
+      </c>
+      <c r="J3" t="n">
+        <v>117573.81</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>KES</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>16217.08</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>P051237141X</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>P051237141X</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>PWANI - WHITE WASH 12X800G GRADE 1</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>31510</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Not Provided</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Vendor Portal</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>976810</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/invoice_data.xlsx
+++ b/invoice_data.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0190977770000011106</t>
+          <t>KRAMWO19202208097777</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2758</v>
+        <v>2758.62</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>80.3500175073075</v>
+        <v>86.95646394310799</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
@@ -710,7 +710,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>

--- a/invoice_data.xlsx
+++ b/invoice_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AJ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,47 +611,47 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INV134440</t>
+          <t>MA109185</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KRAMWO19202208097777</t>
+          <t>KRAMW01 1202206039672</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Frigitec Supplies Ltd</t>
+          <t>Sanpac Africa Limited</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gedion Rhimba Road, Mombasa
-P.O. BOX 2380 - 80100 MOMBASA, KENYA</t>
+          <t>P O Box 20496 - 00200 Nairobi, Kenya
+P O Box 87025 - 80100 Mombasa, Kenya</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TEL: 254. - 41- 2228625 / 2311562 / 2227402
-CELL: +254 - 721 786 440 / +254733 786 440
-Email: sales@frigitec.net</t>
+          <t>Tel: +254 (0)20 2112100/1/2/3
+Cell : +254 (0)733 201 338, (0)722 201 338, (0)756 201 338
+Email: sansales @ sanpac.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24003596</t>
+          <t>24002984</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>17241.38</v>
+        <v>316710</v>
       </c>
       <c r="J2" t="n">
-        <v>20000</v>
+        <v>367383.6</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -659,28 +659,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2758.62</v>
+        <v>50673.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0022503C</t>
+          <t>P051092185B</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>P051096565L</t>
+          <t>P0005943160</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>FPRIGIGAS R22 PB</t>
+          <t>Round Jerryean Yellow 20ltr 800gms</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1530</v>
       </c>
       <c r="Q2" t="n">
-        <v>8620.690000000001</v>
+        <v>185.7</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -694,17 +694,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>C:\Users\hp\Desktop\pwani_finance_01-07-2025\Invoices\FRIGITEC INV134410.pdf</t>
+          <t>C:\Users\hp\Desktop\pwani_finance_01-07-2025\Invoices\SANPAC MA109185.pdf</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>86.95646394310799</v>
+        <v>78.94074383093628</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>17241.38</v>
+        <v>284121</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
@@ -724,6 +724,244 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MA109185</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>KRAMW01 1202206039672</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sanpac Africa Limited</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>P O Box 20496 - 00200 Nairobi, Kenya
+P O Box 87025 - 80100 Mombasa, Kenya</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tel: +254 (0)20 2112100/1/2/3
+Cell : +254 (0)733 201 338, (0)722 201 338, (0)756 201 338
+Email: sansales @ sanpac.com</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>24002984</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>316710</v>
+      </c>
+      <c r="J3" t="n">
+        <v>367383.6</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>KES</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>50673.6</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>P051092185B</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>P0005943160</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Bung Cap &amp; Gasket Sky Blue 10/20ltr</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1530</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Not Provided</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Vendor Portal</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>C:\Users\hp\Desktop\pwani_finance_01-07-2025\Invoices\SANPAC MA109185.pdf</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>85.69148084500091</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>8109</v>
+      </c>
+      <c r="X3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MA109185</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>KRAMW01 1202206039672</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sanpac Africa Limited</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>P O Box 20496 - 00200 Nairobi, Kenya
+P O Box 87025 - 80100 Mombasa, Kenya</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tel: +254 (0)20 2112100/1/2/3
+Cell : +254 (0)733 201 338, (0)722 201 338, (0)756 201 338
+Email: sansales @ sanpac.com</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>24002984</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>316710</v>
+      </c>
+      <c r="J4" t="n">
+        <v>367383.6</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>KES</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>50673.6</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>P051092185B</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>P0005943160</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Woven Bags for 20ltr 95 x 135</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>255</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>96</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Not Provided</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Vendor Portal</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>C:\Users\hp\Desktop\pwani_finance_01-07-2025\Invoices\SANPAC MA109185.pdf</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>84.17803160635005</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>24480</v>
+      </c>
+      <c r="X4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invoice_data.xlsx
+++ b/invoice_data.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MA109185</t>
+          <t>MA109188</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -621,12 +621,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KRAMW01 1202206039672</t>
+          <t>KRAMWO1 1202206039672</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanpac Africa Limited</t>
+          <t>Sanpac Africa Ltd</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -639,7 +639,7 @@
         <is>
           <t>Tel: +254 (0)20 2112100/1/2/3
 Cell : +254 (0)733 201 338, (0)722 201 338, (0)756 201 338
-Email: sansales @ sanpac.com</t>
+Email: sansales@sanpac.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>316710</v>
+        <v>199962</v>
       </c>
       <c r="J2" t="n">
-        <v>367383.6</v>
+        <v>231955.92</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>50673.6</v>
+        <v>31993.92</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>P051092185B</t>
+          <t>P0005943160</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -673,11 +673,11 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Round Jerryean Yellow 20ltr 800gms</t>
+          <t>Round Jerrycan Yellow 20itr 800gms</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1530</v>
+        <v>966</v>
       </c>
       <c r="Q2" t="n">
         <v>185.7</v>
@@ -694,23 +694,23 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>C:\Users\hp\Desktop\pwani_finance_01-07-2025\Invoices\SANPAC MA109185.pdf</t>
+          <t>C:\Users\hp\Desktop\pwani_finance_01-07-2025\Invoices\SANPAC MA109188.pdf</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>78.94074383093628</v>
+        <v>77.85636100504762</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>284121</v>
+        <v>179386.2</v>
       </c>
       <c r="X2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MA109185</t>
+          <t>MA109188</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KRAMW01 1202206039672</t>
+          <t>KRAMWO1 1202206039672</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanpac Africa Limited</t>
+          <t>Sanpac Africa Ltd</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -758,7 +758,7 @@
         <is>
           <t>Tel: +254 (0)20 2112100/1/2/3
 Cell : +254 (0)733 201 338, (0)722 201 338, (0)756 201 338
-Email: sansales @ sanpac.com</t>
+Email: sansales@sanpac.com</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>316710</v>
+        <v>199962</v>
       </c>
       <c r="J3" t="n">
-        <v>367383.6</v>
+        <v>231955.92</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -778,11 +778,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50673.6</v>
+        <v>31993.92</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>P051092185B</t>
+          <t>P0005943160</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1530</v>
+        <v>966</v>
       </c>
       <c r="Q3" t="n">
         <v>5.3</v>
@@ -813,23 +813,23 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>C:\Users\hp\Desktop\pwani_finance_01-07-2025\Invoices\SANPAC MA109185.pdf</t>
+          <t>C:\Users\hp\Desktop\pwani_finance_01-07-2025\Invoices\SANPAC MA109188.pdf</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>85.69148084500091</v>
+        <v>82.04807122358828</v>
       </c>
       <c r="V3" t="n">
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>8109</v>
+        <v>5119.8</v>
       </c>
       <c r="X3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -849,7 +849,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MA109185</t>
+          <t>MA109188</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KRAMW01 1202206039672</t>
+          <t>KRAMWO1 1202206039672</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sanpac Africa Limited</t>
+          <t>Sanpac Africa Ltd</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -877,7 +877,7 @@
         <is>
           <t>Tel: +254 (0)20 2112100/1/2/3
 Cell : +254 (0)733 201 338, (0)722 201 338, (0)756 201 338
-Email: sansales @ sanpac.com</t>
+Email: sansales@sanpac.com</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>316710</v>
+        <v>199962</v>
       </c>
       <c r="J4" t="n">
-        <v>367383.6</v>
+        <v>231955.92</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -897,11 +897,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50673.6</v>
+        <v>31993.92</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>P051092185B</t>
+          <t>P0005943160</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -911,11 +911,11 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Woven Bags for 20ltr 95 x 135</t>
+          <t>Woven Bags for 20Itr 95 x 135</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>255</v>
+        <v>16</v>
       </c>
       <c r="Q4" t="n">
         <v>96</v>
@@ -932,23 +932,23 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>C:\Users\hp\Desktop\pwani_finance_01-07-2025\Invoices\SANPAC MA109185.pdf</t>
+          <t>C:\Users\hp\Desktop\pwani_finance_01-07-2025\Invoices\SANPAC MA109188.pdf</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>84.17803160635005</v>
+        <v>77.94251106261639</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>24480</v>
+        <v>1536</v>
       </c>
       <c r="X4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
